--- a/artfynd/A 20225-2026 artfynd.xlsx
+++ b/artfynd/A 20225-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133883277</v>
+        <v>133883461</v>
       </c>
       <c r="B2" t="n">
         <v>99181</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521338</v>
+        <v>521495</v>
       </c>
       <c r="R2" t="n">
-        <v>6953912</v>
+        <v>6953868</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133883454</v>
+        <v>133883277</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>99181</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521722</v>
+        <v>521338</v>
       </c>
       <c r="R3" t="n">
-        <v>6954031</v>
+        <v>6953912</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133883461</v>
+        <v>133883256</v>
       </c>
       <c r="B4" t="n">
-        <v>99181</v>
+        <v>91960</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521495</v>
+        <v>521353</v>
       </c>
       <c r="R4" t="n">
-        <v>6953868</v>
+        <v>6953801</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133883256</v>
+        <v>133883263</v>
       </c>
       <c r="B5" t="n">
-        <v>91960</v>
+        <v>99181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521353</v>
+        <v>521802</v>
       </c>
       <c r="R5" t="n">
-        <v>6953801</v>
+        <v>6954024</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1042,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ca 10 plantor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133883477</v>
+        <v>133883489</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>99181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521295</v>
+        <v>521314</v>
       </c>
       <c r="R6" t="n">
-        <v>6953845</v>
+        <v>6953955</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1170,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133883447</v>
+        <v>133883456</v>
       </c>
       <c r="B7" t="n">
-        <v>57975</v>
+        <v>80474</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1205,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521330</v>
+        <v>521555</v>
       </c>
       <c r="R7" t="n">
-        <v>6953791</v>
+        <v>6953861</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1241,11 +1236,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1272,7 +1262,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133883263</v>
+        <v>133883237</v>
       </c>
       <c r="B8" t="n">
         <v>99181</v>
@@ -1307,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521802</v>
+        <v>521548</v>
       </c>
       <c r="R8" t="n">
-        <v>6954024</v>
+        <v>6953980</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1374,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133883456</v>
+        <v>133883248</v>
       </c>
       <c r="B9" t="n">
-        <v>80474</v>
+        <v>99181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1409,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521555</v>
+        <v>521340</v>
       </c>
       <c r="R9" t="n">
-        <v>6953861</v>
+        <v>6953933</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1445,6 +1435,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Över 20 plantor</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,32 +1466,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133883479</v>
+        <v>133883495</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>99181</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1506,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521274</v>
+        <v>521293</v>
       </c>
       <c r="R10" t="n">
-        <v>6953884</v>
+        <v>6953926</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1542,11 +1537,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1573,32 +1563,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133883489</v>
+        <v>133883278</v>
       </c>
       <c r="B11" t="n">
-        <v>99181</v>
+        <v>79359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1608,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521314</v>
+        <v>521295</v>
       </c>
       <c r="R11" t="n">
-        <v>6953955</v>
+        <v>6953965</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1670,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133883237</v>
+        <v>133883249</v>
       </c>
       <c r="B12" t="n">
-        <v>99181</v>
+        <v>79359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1705,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521548</v>
+        <v>521358</v>
       </c>
       <c r="R12" t="n">
-        <v>6953980</v>
+        <v>6953923</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1745,7 +1735,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ca 10 plantor</t>
+          <t>60 cm lång</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1772,32 +1762,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133883248</v>
+        <v>133883469</v>
       </c>
       <c r="B13" t="n">
-        <v>99181</v>
+        <v>79359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1807,10 +1797,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521340</v>
+        <v>521326</v>
       </c>
       <c r="R13" t="n">
-        <v>6953933</v>
+        <v>6953902</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1843,11 +1833,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Över 20 plantor</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1874,32 +1859,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133883278</v>
+        <v>133883238</v>
       </c>
       <c r="B14" t="n">
-        <v>79359</v>
+        <v>99181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1909,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521295</v>
+        <v>521504</v>
       </c>
       <c r="R14" t="n">
-        <v>6953965</v>
+        <v>6953992</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1971,7 +1956,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133883249</v>
+        <v>133883468</v>
       </c>
       <c r="B15" t="n">
         <v>79359</v>
@@ -2006,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521358</v>
+        <v>521363</v>
       </c>
       <c r="R15" t="n">
-        <v>6953923</v>
+        <v>6953837</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2042,11 +2027,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>60 cm lång</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2073,7 +2053,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133883495</v>
+        <v>133883239</v>
       </c>
       <c r="B16" t="n">
         <v>99181</v>
@@ -2108,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>521293</v>
+        <v>521519</v>
       </c>
       <c r="R16" t="n">
-        <v>6953926</v>
+        <v>6954006</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2170,27 +2150,27 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133883469</v>
+        <v>133883472</v>
       </c>
       <c r="B17" t="n">
-        <v>79359</v>
+        <v>80485</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2205,10 +2185,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>521326</v>
+        <v>521554</v>
       </c>
       <c r="R17" t="n">
-        <v>6953902</v>
+        <v>6953860</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2267,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133883453</v>
+        <v>133883467</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2278,21 +2258,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2302,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521710</v>
+        <v>521324</v>
       </c>
       <c r="R18" t="n">
-        <v>6954038</v>
+        <v>6953800</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2338,11 +2318,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2369,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133883468</v>
+        <v>133883455</v>
       </c>
       <c r="B19" t="n">
-        <v>79359</v>
+        <v>80474</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2380,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2404,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>521363</v>
+        <v>521575</v>
       </c>
       <c r="R19" t="n">
-        <v>6953837</v>
+        <v>6953947</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2466,7 +2441,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133883238</v>
+        <v>133883280</v>
       </c>
       <c r="B20" t="n">
         <v>99181</v>
@@ -2501,10 +2476,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521504</v>
+        <v>521531</v>
       </c>
       <c r="R20" t="n">
-        <v>6953992</v>
+        <v>6954025</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2563,32 +2538,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133883472</v>
+        <v>133883253</v>
       </c>
       <c r="B21" t="n">
-        <v>80485</v>
+        <v>99181</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2598,10 +2573,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521554</v>
+        <v>521349</v>
       </c>
       <c r="R21" t="n">
-        <v>6953860</v>
+        <v>6953818</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2634,6 +2609,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ca 10 plantor</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2660,7 +2640,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133883280</v>
+        <v>133883496</v>
       </c>
       <c r="B22" t="n">
         <v>99181</v>
@@ -2695,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521531</v>
+        <v>521496</v>
       </c>
       <c r="R22" t="n">
-        <v>6954025</v>
+        <v>6954039</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2731,6 +2711,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2757,32 +2742,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133883467</v>
+        <v>133883459</v>
       </c>
       <c r="B23" t="n">
-        <v>79359</v>
+        <v>99181</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2792,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521324</v>
+        <v>521807</v>
       </c>
       <c r="R23" t="n">
-        <v>6953800</v>
+        <v>6954021</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2828,6 +2813,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>24st bladrosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2854,10 +2844,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133883448</v>
+        <v>133883446</v>
       </c>
       <c r="B24" t="n">
-        <v>57975</v>
+        <v>79978</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2865,21 +2855,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2889,10 +2879,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>521654</v>
+        <v>521332</v>
       </c>
       <c r="R24" t="n">
-        <v>6954074</v>
+        <v>6953999</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,11 +2915,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2956,32 +2941,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133883239</v>
+        <v>133883240</v>
       </c>
       <c r="B25" t="n">
-        <v>99181</v>
+        <v>78368</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2991,10 +2976,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521519</v>
+        <v>521525</v>
       </c>
       <c r="R25" t="n">
-        <v>6954006</v>
+        <v>6954019</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3053,10 +3038,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133883455</v>
+        <v>133883244</v>
       </c>
       <c r="B26" t="n">
-        <v>80474</v>
+        <v>79359</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3064,21 +3049,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3088,10 +3073,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>521575</v>
+        <v>521364</v>
       </c>
       <c r="R26" t="n">
-        <v>6953947</v>
+        <v>6954001</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3150,10 +3135,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133883452</v>
+        <v>133883242</v>
       </c>
       <c r="B27" t="n">
-        <v>57975</v>
+        <v>83208</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3161,21 +3146,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3185,10 +3170,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521714</v>
+        <v>521529</v>
       </c>
       <c r="R27" t="n">
-        <v>6954038</v>
+        <v>6954026</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3223,17 +3208,13 @@
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3252,32 +3233,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133883253</v>
+        <v>133883245</v>
       </c>
       <c r="B28" t="n">
-        <v>99181</v>
+        <v>78368</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3287,10 +3268,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521349</v>
+        <v>521357</v>
       </c>
       <c r="R28" t="n">
-        <v>6953818</v>
+        <v>6953972</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3323,11 +3304,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ca 10 plantor</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3354,32 +3330,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133883496</v>
+        <v>133883284</v>
       </c>
       <c r="B29" t="n">
-        <v>99181</v>
+        <v>93295</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3389,10 +3365,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521496</v>
+        <v>521587</v>
       </c>
       <c r="R29" t="n">
-        <v>6954039</v>
+        <v>6953983</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3425,11 +3401,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3456,45 +3427,57 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133883446</v>
+        <v>133883497</v>
       </c>
       <c r="B30" t="n">
-        <v>79978</v>
+        <v>57165</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>102613</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>ruvande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kojviken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521332</v>
+        <v>521278</v>
       </c>
       <c r="R30" t="n">
-        <v>6953999</v>
+        <v>6953952</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3553,32 +3536,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133883240</v>
+        <v>133883494</v>
       </c>
       <c r="B31" t="n">
-        <v>78368</v>
+        <v>99181</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3588,10 +3571,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521525</v>
+        <v>521511</v>
       </c>
       <c r="R31" t="n">
-        <v>6954019</v>
+        <v>6953850</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3650,45 +3633,57 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133883234</v>
+        <v>133883487</v>
       </c>
       <c r="B32" t="n">
-        <v>57975</v>
+        <v>99181</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kojviken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521776</v>
+        <v>521273</v>
       </c>
       <c r="R32" t="n">
-        <v>6954013</v>
+        <v>6953919</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3725,7 +3720,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på gran</t>
+          <t>Minst 200</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3734,6 +3729,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3752,7 +3748,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133883459</v>
+        <v>133883254</v>
       </c>
       <c r="B33" t="n">
         <v>99181</v>
@@ -3787,10 +3783,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521807</v>
+        <v>521351</v>
       </c>
       <c r="R33" t="n">
-        <v>6954021</v>
+        <v>6953815</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3827,7 +3823,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>24st bladrosetter</t>
+          <t>20 plantor ca</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3854,32 +3850,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133883244</v>
+        <v>133883488</v>
       </c>
       <c r="B34" t="n">
-        <v>79359</v>
+        <v>99181</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3889,10 +3885,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>521364</v>
+        <v>521301</v>
       </c>
       <c r="R34" t="n">
-        <v>6954001</v>
+        <v>6953960</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3951,32 +3947,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133883284</v>
+        <v>133883484</v>
       </c>
       <c r="B35" t="n">
-        <v>93295</v>
+        <v>99181</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3986,10 +3982,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521587</v>
+        <v>521420</v>
       </c>
       <c r="R35" t="n">
-        <v>6953983</v>
+        <v>6953892</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4048,32 +4044,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133883245</v>
+        <v>133883458</v>
       </c>
       <c r="B36" t="n">
-        <v>78368</v>
+        <v>99181</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4083,10 +4079,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521357</v>
+        <v>521417</v>
       </c>
       <c r="R36" t="n">
-        <v>6953972</v>
+        <v>6954029</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4119,6 +4115,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>21st bladrosetter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4145,32 +4146,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133883242</v>
+        <v>133883490</v>
       </c>
       <c r="B37" t="n">
-        <v>83208</v>
+        <v>99181</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4180,10 +4181,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>521529</v>
+        <v>521336</v>
       </c>
       <c r="R37" t="n">
-        <v>6954026</v>
+        <v>6953957</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4218,13 +4219,17 @@
           <t>2026-05-15</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4243,57 +4248,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133883487</v>
+        <v>133883241</v>
       </c>
       <c r="B38" t="n">
-        <v>99181</v>
+        <v>83344</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Kojviken, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521273</v>
+        <v>521529</v>
       </c>
       <c r="R38" t="n">
-        <v>6953919</v>
+        <v>6954026</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4328,18 +4321,12 @@
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Minst 200</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4358,7 +4345,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133883254</v>
+        <v>133883493</v>
       </c>
       <c r="B39" t="n">
         <v>99181</v>
@@ -4393,10 +4380,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>521351</v>
+        <v>521488</v>
       </c>
       <c r="R39" t="n">
-        <v>6953815</v>
+        <v>6954062</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4429,11 +4416,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>20 plantor ca</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4460,57 +4442,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133883497</v>
+        <v>133883279</v>
       </c>
       <c r="B40" t="n">
-        <v>57165</v>
+        <v>80474</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102613</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>ruvande</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kojviken, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>521278</v>
+        <v>521406</v>
       </c>
       <c r="R40" t="n">
-        <v>6953952</v>
+        <v>6954071</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4569,32 +4539,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133883494</v>
+        <v>133883260</v>
       </c>
       <c r="B41" t="n">
-        <v>99181</v>
+        <v>80474</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4604,10 +4574,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>521511</v>
+        <v>521547</v>
       </c>
       <c r="R41" t="n">
-        <v>6953850</v>
+        <v>6953862</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4640,6 +4610,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4666,7 +4641,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133883488</v>
+        <v>133883463</v>
       </c>
       <c r="B42" t="n">
         <v>99181</v>
@@ -4694,17 +4669,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kojviken, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>521301</v>
+        <v>521538</v>
       </c>
       <c r="R42" t="n">
-        <v>6953960</v>
+        <v>6953983</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4739,12 +4726,18 @@
           <t>2026-05-15</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>&gt;100st bladrosetter</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4763,32 +4756,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133883458</v>
+        <v>133883261</v>
       </c>
       <c r="B43" t="n">
-        <v>99181</v>
+        <v>80474</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4798,10 +4791,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>521417</v>
+        <v>521691</v>
       </c>
       <c r="R43" t="n">
-        <v>6954029</v>
+        <v>6953987</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4838,7 +4831,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>21st bladrosetter</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4865,32 +4858,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133883490</v>
+        <v>133883470</v>
       </c>
       <c r="B44" t="n">
-        <v>99181</v>
+        <v>83208</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4900,10 +4893,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>521336</v>
+        <v>521285</v>
       </c>
       <c r="R44" t="n">
-        <v>6953957</v>
+        <v>6953964</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4936,11 +4929,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4967,7 +4955,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133883484</v>
+        <v>133883486</v>
       </c>
       <c r="B45" t="n">
         <v>99181</v>
@@ -5002,10 +4990,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>521420</v>
+        <v>521407</v>
       </c>
       <c r="R45" t="n">
-        <v>6953892</v>
+        <v>6953853</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5064,7 +5052,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133883493</v>
+        <v>133883460</v>
       </c>
       <c r="B46" t="n">
         <v>99181</v>
@@ -5099,10 +5087,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>521488</v>
+        <v>521807</v>
       </c>
       <c r="R46" t="n">
-        <v>6954062</v>
+        <v>6954020</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5135,6 +5123,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5161,32 +5154,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133883260</v>
+        <v>133883246</v>
       </c>
       <c r="B47" t="n">
-        <v>80474</v>
+        <v>99181</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5196,10 +5189,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>521547</v>
+        <v>521328</v>
       </c>
       <c r="R47" t="n">
-        <v>6953862</v>
+        <v>6953954</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5236,7 +5229,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>7 plantor</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5263,32 +5256,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133883241</v>
+        <v>133883462</v>
       </c>
       <c r="B48" t="n">
-        <v>83344</v>
+        <v>99181</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5298,10 +5291,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>521529</v>
+        <v>521356</v>
       </c>
       <c r="R48" t="n">
-        <v>6954026</v>
+        <v>6954020</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5334,6 +5327,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>7st bladrosetter</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5360,32 +5358,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133883279</v>
+        <v>133883471</v>
       </c>
       <c r="B49" t="n">
-        <v>80474</v>
+        <v>93257</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5395,10 +5393,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>521406</v>
+        <v>521401</v>
       </c>
       <c r="R49" t="n">
-        <v>6954071</v>
+        <v>6953862</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5457,7 +5455,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133883463</v>
+        <v>133883250</v>
       </c>
       <c r="B50" t="n">
         <v>99181</v>
@@ -5485,29 +5483,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kojviken, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>521538</v>
+        <v>521352</v>
       </c>
       <c r="R50" t="n">
-        <v>6953983</v>
+        <v>6953865</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5544,7 +5530,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>&gt;100st bladrosetter</t>
+          <t>Över 10 plantor</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5553,7 +5539,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5572,32 +5557,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133883261</v>
+        <v>133883465</v>
       </c>
       <c r="B51" t="n">
-        <v>80474</v>
+        <v>99181</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5607,10 +5592,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>521691</v>
+        <v>521548</v>
       </c>
       <c r="R51" t="n">
-        <v>6953987</v>
+        <v>6953962</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5647,7 +5632,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>3st bladrosetter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5674,10 +5659,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133883470</v>
+        <v>133883252</v>
       </c>
       <c r="B52" t="n">
-        <v>83208</v>
+        <v>79359</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5685,21 +5670,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5709,10 +5694,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>521285</v>
+        <v>521347</v>
       </c>
       <c r="R52" t="n">
-        <v>6953964</v>
+        <v>6953820</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5771,10 +5756,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133883449</v>
+        <v>133883275</v>
       </c>
       <c r="B53" t="n">
-        <v>57975</v>
+        <v>79978</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5782,21 +5767,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5806,10 +5791,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>521652</v>
+        <v>521472</v>
       </c>
       <c r="R53" t="n">
-        <v>6954080</v>
+        <v>6953894</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5842,11 +5827,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5873,32 +5853,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133883476</v>
+        <v>133883259</v>
       </c>
       <c r="B54" t="n">
-        <v>57975</v>
+        <v>101389</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5908,10 +5888,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>521309</v>
+        <v>521380</v>
       </c>
       <c r="R54" t="n">
-        <v>6953828</v>
+        <v>6953811</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5944,11 +5924,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5975,7 +5950,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133883486</v>
+        <v>133883281</v>
       </c>
       <c r="B55" t="n">
         <v>99181</v>
@@ -6010,10 +5985,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>521407</v>
+        <v>521518</v>
       </c>
       <c r="R55" t="n">
-        <v>6953853</v>
+        <v>6954017</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6072,7 +6047,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133883460</v>
+        <v>133883457</v>
       </c>
       <c r="B56" t="n">
         <v>99181</v>
@@ -6107,10 +6082,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>521807</v>
+        <v>521412</v>
       </c>
       <c r="R56" t="n">
-        <v>6954020</v>
+        <v>6954018</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6147,7 +6122,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>5st bladrosetter</t>
+          <t>15st bladrosetter</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6174,32 +6149,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133883246</v>
+        <v>133883466</v>
       </c>
       <c r="B57" t="n">
-        <v>99181</v>
+        <v>79359</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6209,10 +6184,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>521328</v>
+        <v>521385</v>
       </c>
       <c r="R57" t="n">
-        <v>6953954</v>
+        <v>6953844</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6245,11 +6220,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>7 plantor</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6276,32 +6246,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133883462</v>
+        <v>133883243</v>
       </c>
       <c r="B58" t="n">
-        <v>99181</v>
+        <v>79116</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6311,10 +6281,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>521356</v>
+        <v>521416</v>
       </c>
       <c r="R58" t="n">
-        <v>6954020</v>
+        <v>6954025</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6347,11 +6317,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>7st bladrosetter</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6378,32 +6343,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133883480</v>
+        <v>133883282</v>
       </c>
       <c r="B59" t="n">
-        <v>57975</v>
+        <v>99181</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6413,10 +6378,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>521272</v>
+        <v>521518</v>
       </c>
       <c r="R59" t="n">
-        <v>6953892</v>
+        <v>6953983</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6449,11 +6414,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6480,32 +6440,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133883250</v>
+        <v>133883247</v>
       </c>
       <c r="B60" t="n">
-        <v>99181</v>
+        <v>79359</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6515,10 +6475,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>521352</v>
+        <v>521336</v>
       </c>
       <c r="R60" t="n">
-        <v>6953865</v>
+        <v>6953943</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6551,11 +6511,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Över 10 plantor</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6582,32 +6537,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133883471</v>
+        <v>133883258</v>
       </c>
       <c r="B61" t="n">
-        <v>93257</v>
+        <v>99181</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6617,10 +6572,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>521401</v>
+        <v>521357</v>
       </c>
       <c r="R61" t="n">
-        <v>6953862</v>
+        <v>6953811</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6653,6 +6608,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Över 20 plantor</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6679,32 +6639,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133883450</v>
+        <v>133883491</v>
       </c>
       <c r="B62" t="n">
-        <v>57975</v>
+        <v>99181</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6714,10 +6674,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>521664</v>
+        <v>521351</v>
       </c>
       <c r="R62" t="n">
-        <v>6954069</v>
+        <v>6953981</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6754,7 +6714,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Minst 40</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6781,7 +6741,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133883451</v>
+        <v>133883454</v>
       </c>
       <c r="B63" t="n">
         <v>57975</v>
@@ -6816,10 +6776,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>521703</v>
+        <v>521722</v>
       </c>
       <c r="R63" t="n">
-        <v>6954046</v>
+        <v>6954031</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6883,32 +6843,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133883465</v>
+        <v>133883477</v>
       </c>
       <c r="B64" t="n">
-        <v>99181</v>
+        <v>57975</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6918,10 +6878,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>521548</v>
+        <v>521295</v>
       </c>
       <c r="R64" t="n">
-        <v>6953962</v>
+        <v>6953845</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6958,7 +6918,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>3st bladrosetter</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6985,32 +6945,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133883457</v>
+        <v>133883447</v>
       </c>
       <c r="B65" t="n">
-        <v>99181</v>
+        <v>57975</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7020,10 +6980,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>521412</v>
+        <v>521330</v>
       </c>
       <c r="R65" t="n">
-        <v>6954018</v>
+        <v>6953791</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7060,7 +7020,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>15st bladrosetter</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7087,32 +7047,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133883281</v>
+        <v>133883479</v>
       </c>
       <c r="B66" t="n">
-        <v>99181</v>
+        <v>57975</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7122,10 +7082,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>521518</v>
+        <v>521274</v>
       </c>
       <c r="R66" t="n">
-        <v>6954017</v>
+        <v>6953884</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7158,6 +7118,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7184,32 +7149,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133883259</v>
+        <v>133883453</v>
       </c>
       <c r="B67" t="n">
-        <v>101389</v>
+        <v>57975</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7219,10 +7184,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>521380</v>
+        <v>521710</v>
       </c>
       <c r="R67" t="n">
-        <v>6953811</v>
+        <v>6954038</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7255,6 +7220,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7281,10 +7251,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133883275</v>
+        <v>133883448</v>
       </c>
       <c r="B68" t="n">
-        <v>79978</v>
+        <v>57975</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7292,21 +7262,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7316,10 +7286,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>521472</v>
+        <v>521654</v>
       </c>
       <c r="R68" t="n">
-        <v>6953894</v>
+        <v>6954074</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7352,6 +7322,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7378,10 +7353,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133883252</v>
+        <v>133883452</v>
       </c>
       <c r="B69" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7389,21 +7364,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7413,10 +7388,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>521347</v>
+        <v>521714</v>
       </c>
       <c r="R69" t="n">
-        <v>6953820</v>
+        <v>6954038</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7449,6 +7424,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7475,10 +7455,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133883466</v>
+        <v>133883234</v>
       </c>
       <c r="B70" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7486,21 +7466,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7510,10 +7490,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>521385</v>
+        <v>521776</v>
       </c>
       <c r="R70" t="n">
-        <v>6953844</v>
+        <v>6954013</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7546,6 +7526,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7572,10 +7557,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133883243</v>
+        <v>133883449</v>
       </c>
       <c r="B71" t="n">
-        <v>79116</v>
+        <v>57975</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7583,21 +7568,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7607,10 +7592,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>521416</v>
+        <v>521652</v>
       </c>
       <c r="R71" t="n">
-        <v>6954025</v>
+        <v>6954080</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7643,6 +7628,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7669,7 +7659,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133883483</v>
+        <v>133883476</v>
       </c>
       <c r="B72" t="n">
         <v>57975</v>
@@ -7704,10 +7694,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>521749</v>
+        <v>521309</v>
       </c>
       <c r="R72" t="n">
-        <v>6954025</v>
+        <v>6953828</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7744,7 +7734,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7771,32 +7761,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133883282</v>
+        <v>133883480</v>
       </c>
       <c r="B73" t="n">
-        <v>99181</v>
+        <v>57975</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7806,10 +7796,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>521518</v>
+        <v>521272</v>
       </c>
       <c r="R73" t="n">
-        <v>6953983</v>
+        <v>6953892</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7842,6 +7832,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7868,10 +7863,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133883247</v>
+        <v>133883450</v>
       </c>
       <c r="B74" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7879,21 +7874,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7903,10 +7898,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>521336</v>
+        <v>521664</v>
       </c>
       <c r="R74" t="n">
-        <v>6953943</v>
+        <v>6954069</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7939,6 +7934,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7965,32 +7965,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133883258</v>
+        <v>133883451</v>
       </c>
       <c r="B75" t="n">
-        <v>99181</v>
+        <v>57975</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8000,10 +8000,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>521357</v>
+        <v>521703</v>
       </c>
       <c r="R75" t="n">
-        <v>6953811</v>
+        <v>6954046</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8040,7 +8040,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Över 20 plantor</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8067,7 +8067,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133883482</v>
+        <v>133883483</v>
       </c>
       <c r="B76" t="n">
         <v>57975</v>
@@ -8102,10 +8102,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>521755</v>
+        <v>521749</v>
       </c>
       <c r="R76" t="n">
-        <v>6954023</v>
+        <v>6954025</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8142,7 +8142,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8169,32 +8169,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133883491</v>
+        <v>133883482</v>
       </c>
       <c r="B77" t="n">
-        <v>99181</v>
+        <v>57975</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8204,10 +8204,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>521351</v>
+        <v>521755</v>
       </c>
       <c r="R77" t="n">
-        <v>6953981</v>
+        <v>6954023</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Minst 40</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD77" t="b">

--- a/artfynd/A 20225-2026 artfynd.xlsx
+++ b/artfynd/A 20225-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133883461</v>
       </c>
       <c r="B2" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133883277</v>
+        <v>133883256</v>
       </c>
       <c r="B3" t="n">
-        <v>99181</v>
+        <v>91967</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521338</v>
+        <v>521353</v>
       </c>
       <c r="R3" t="n">
-        <v>6953912</v>
+        <v>6953801</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133883256</v>
+        <v>133883277</v>
       </c>
       <c r="B4" t="n">
-        <v>91960</v>
+        <v>99188</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521353</v>
+        <v>521338</v>
       </c>
       <c r="R4" t="n">
-        <v>6953801</v>
+        <v>6953912</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133883263</v>
+        <v>133883489</v>
       </c>
       <c r="B5" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521802</v>
+        <v>521314</v>
       </c>
       <c r="R5" t="n">
-        <v>6954024</v>
+        <v>6953955</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ca 10 plantor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133883489</v>
+        <v>133883456</v>
       </c>
       <c r="B6" t="n">
-        <v>99181</v>
+        <v>80481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521314</v>
+        <v>521555</v>
       </c>
       <c r="R6" t="n">
-        <v>6953955</v>
+        <v>6953861</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1165,32 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133883456</v>
+        <v>133883263</v>
       </c>
       <c r="B7" t="n">
-        <v>80474</v>
+        <v>99188</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521555</v>
+        <v>521802</v>
       </c>
       <c r="R7" t="n">
-        <v>6953861</v>
+        <v>6954024</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,6 +1231,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ca 10 plantor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1265,7 +1265,7 @@
         <v>133883237</v>
       </c>
       <c r="B8" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>133883248</v>
       </c>
       <c r="B9" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>133883495</v>
       </c>
       <c r="B10" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>133883278</v>
       </c>
       <c r="B11" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         <v>133883249</v>
       </c>
       <c r="B12" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         <v>133883469</v>
       </c>
       <c r="B13" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1859,32 +1859,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133883238</v>
+        <v>133883468</v>
       </c>
       <c r="B14" t="n">
-        <v>99181</v>
+        <v>79366</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521504</v>
+        <v>521363</v>
       </c>
       <c r="R14" t="n">
-        <v>6953992</v>
+        <v>6953837</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1956,32 +1956,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133883468</v>
+        <v>133883238</v>
       </c>
       <c r="B15" t="n">
-        <v>79359</v>
+        <v>99188</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1991,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521363</v>
+        <v>521504</v>
       </c>
       <c r="R15" t="n">
-        <v>6953837</v>
+        <v>6953992</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,32 +2053,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133883239</v>
+        <v>133883472</v>
       </c>
       <c r="B16" t="n">
-        <v>99181</v>
+        <v>80492</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>521519</v>
+        <v>521554</v>
       </c>
       <c r="R16" t="n">
-        <v>6954006</v>
+        <v>6953860</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2150,32 +2150,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133883472</v>
+        <v>133883280</v>
       </c>
       <c r="B17" t="n">
-        <v>80485</v>
+        <v>99188</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2185,10 +2185,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>521554</v>
+        <v>521531</v>
       </c>
       <c r="R17" t="n">
-        <v>6953860</v>
+        <v>6954025</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2247,32 +2247,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133883467</v>
+        <v>133883253</v>
       </c>
       <c r="B18" t="n">
-        <v>79359</v>
+        <v>99188</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521324</v>
+        <v>521349</v>
       </c>
       <c r="R18" t="n">
-        <v>6953800</v>
+        <v>6953818</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2318,6 +2318,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ca 10 plantor</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2344,10 +2349,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133883455</v>
+        <v>133883467</v>
       </c>
       <c r="B19" t="n">
-        <v>80474</v>
+        <v>79366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2360,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>521575</v>
+        <v>521324</v>
       </c>
       <c r="R19" t="n">
-        <v>6953947</v>
+        <v>6953800</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2441,32 +2446,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133883280</v>
+        <v>133883455</v>
       </c>
       <c r="B20" t="n">
-        <v>99181</v>
+        <v>80481</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2476,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521531</v>
+        <v>521575</v>
       </c>
       <c r="R20" t="n">
-        <v>6954025</v>
+        <v>6953947</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2538,10 +2543,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133883253</v>
+        <v>133883239</v>
       </c>
       <c r="B21" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2573,10 +2578,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521349</v>
+        <v>521519</v>
       </c>
       <c r="R21" t="n">
-        <v>6953818</v>
+        <v>6954006</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2609,11 +2614,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ca 10 plantor</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2640,32 +2640,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133883496</v>
+        <v>133883240</v>
       </c>
       <c r="B22" t="n">
-        <v>99181</v>
+        <v>78375</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>228579</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521496</v>
+        <v>521525</v>
       </c>
       <c r="R22" t="n">
-        <v>6954039</v>
+        <v>6954019</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2711,11 +2711,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2742,10 +2737,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133883459</v>
+        <v>133883496</v>
       </c>
       <c r="B23" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2777,10 +2772,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521807</v>
+        <v>521496</v>
       </c>
       <c r="R23" t="n">
-        <v>6954021</v>
+        <v>6954039</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2817,7 +2812,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>24st bladrosetter</t>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2847,7 +2842,7 @@
         <v>133883446</v>
       </c>
       <c r="B24" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2941,32 +2936,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133883240</v>
+        <v>133883459</v>
       </c>
       <c r="B25" t="n">
-        <v>78368</v>
+        <v>99188</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228579</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2976,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521525</v>
+        <v>521807</v>
       </c>
       <c r="R25" t="n">
-        <v>6954019</v>
+        <v>6954021</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3012,6 +3007,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>24st bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3041,7 +3041,7 @@
         <v>133883244</v>
       </c>
       <c r="B26" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3135,10 +3135,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133883242</v>
+        <v>133883284</v>
       </c>
       <c r="B27" t="n">
-        <v>83208</v>
+        <v>93302</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3146,21 +3146,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>5966</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3170,10 +3170,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521529</v>
+        <v>521587</v>
       </c>
       <c r="R27" t="n">
-        <v>6954026</v>
+        <v>6953983</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3214,7 +3214,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3233,10 +3232,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133883245</v>
+        <v>133883242</v>
       </c>
       <c r="B28" t="n">
-        <v>78368</v>
+        <v>83215</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3244,21 +3243,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228579</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3268,10 +3267,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521357</v>
+        <v>521529</v>
       </c>
       <c r="R28" t="n">
-        <v>6953972</v>
+        <v>6954026</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3312,6 +3311,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3330,10 +3330,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133883284</v>
+        <v>133883245</v>
       </c>
       <c r="B29" t="n">
-        <v>93295</v>
+        <v>78375</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3341,21 +3341,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5966</v>
+        <v>228579</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521587</v>
+        <v>521357</v>
       </c>
       <c r="R29" t="n">
-        <v>6953983</v>
+        <v>6953972</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3427,57 +3427,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133883497</v>
+        <v>133883494</v>
       </c>
       <c r="B30" t="n">
-        <v>57165</v>
+        <v>99188</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102613</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>ruvande</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kojviken, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521278</v>
+        <v>521511</v>
       </c>
       <c r="R30" t="n">
-        <v>6953952</v>
+        <v>6953850</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3536,10 +3524,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133883494</v>
+        <v>133883487</v>
       </c>
       <c r="B31" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3564,17 +3552,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kojviken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521511</v>
+        <v>521273</v>
       </c>
       <c r="R31" t="n">
-        <v>6953850</v>
+        <v>6953919</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3609,12 +3609,18 @@
           <t>2026-05-15</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Minst 200</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3633,10 +3639,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133883487</v>
+        <v>133883254</v>
       </c>
       <c r="B32" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3661,29 +3667,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kojviken, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521273</v>
+        <v>521351</v>
       </c>
       <c r="R32" t="n">
-        <v>6953919</v>
+        <v>6953815</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3720,7 +3714,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Minst 200</t>
+          <t>20 plantor ca</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3729,7 +3723,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3748,45 +3741,57 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133883254</v>
+        <v>133883497</v>
       </c>
       <c r="B33" t="n">
-        <v>99181</v>
+        <v>57165</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>102613</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>ruvande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kojviken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521351</v>
+        <v>521278</v>
       </c>
       <c r="R33" t="n">
-        <v>6953815</v>
+        <v>6953952</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3819,11 +3824,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>20 plantor ca</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3850,10 +3850,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133883488</v>
+        <v>133883458</v>
       </c>
       <c r="B34" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>521301</v>
+        <v>521417</v>
       </c>
       <c r="R34" t="n">
-        <v>6953960</v>
+        <v>6954029</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3921,6 +3921,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>21st bladrosetter</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3947,10 +3952,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133883484</v>
+        <v>133883490</v>
       </c>
       <c r="B35" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3982,10 +3987,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521420</v>
+        <v>521336</v>
       </c>
       <c r="R35" t="n">
-        <v>6953892</v>
+        <v>6953957</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4018,6 +4023,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4044,10 +4054,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133883458</v>
+        <v>133883484</v>
       </c>
       <c r="B36" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4079,10 +4089,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521417</v>
+        <v>521420</v>
       </c>
       <c r="R36" t="n">
-        <v>6954029</v>
+        <v>6953892</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4115,11 +4125,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>21st bladrosetter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4146,10 +4151,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133883490</v>
+        <v>133883488</v>
       </c>
       <c r="B37" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4181,10 +4186,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>521336</v>
+        <v>521301</v>
       </c>
       <c r="R37" t="n">
-        <v>6953957</v>
+        <v>6953960</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4217,11 +4222,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4248,10 +4248,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133883241</v>
+        <v>133883260</v>
       </c>
       <c r="B38" t="n">
-        <v>83344</v>
+        <v>80481</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4259,21 +4259,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521529</v>
+        <v>521547</v>
       </c>
       <c r="R38" t="n">
-        <v>6954026</v>
+        <v>6953862</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4319,6 +4319,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4345,32 +4350,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133883493</v>
+        <v>133883241</v>
       </c>
       <c r="B39" t="n">
-        <v>99181</v>
+        <v>83351</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4380,10 +4385,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>521488</v>
+        <v>521529</v>
       </c>
       <c r="R39" t="n">
-        <v>6954062</v>
+        <v>6954026</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4445,7 +4450,7 @@
         <v>133883279</v>
       </c>
       <c r="B40" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4539,32 +4544,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133883260</v>
+        <v>133883493</v>
       </c>
       <c r="B41" t="n">
-        <v>80474</v>
+        <v>99188</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4574,10 +4579,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>521547</v>
+        <v>521488</v>
       </c>
       <c r="R41" t="n">
-        <v>6953862</v>
+        <v>6954062</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4610,11 +4615,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4644,7 +4644,7 @@
         <v>133883463</v>
       </c>
       <c r="B42" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4759,7 +4759,7 @@
         <v>133883261</v>
       </c>
       <c r="B43" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4861,7 +4861,7 @@
         <v>133883470</v>
       </c>
       <c r="B44" t="n">
-        <v>83208</v>
+        <v>83215</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4955,10 +4955,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133883486</v>
+        <v>133883460</v>
       </c>
       <c r="B45" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4990,10 +4990,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>521407</v>
+        <v>521807</v>
       </c>
       <c r="R45" t="n">
-        <v>6953853</v>
+        <v>6954020</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5026,6 +5026,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5052,10 +5057,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133883460</v>
+        <v>133883246</v>
       </c>
       <c r="B46" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5087,10 +5092,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>521807</v>
+        <v>521328</v>
       </c>
       <c r="R46" t="n">
-        <v>6954020</v>
+        <v>6953954</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5127,7 +5132,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>5st bladrosetter</t>
+          <t>7 plantor</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5154,10 +5159,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133883246</v>
+        <v>133883486</v>
       </c>
       <c r="B47" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5189,10 +5194,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>521328</v>
+        <v>521407</v>
       </c>
       <c r="R47" t="n">
-        <v>6953954</v>
+        <v>6953853</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5225,11 +5230,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>7 plantor</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5259,7 +5259,7 @@
         <v>133883462</v>
       </c>
       <c r="B48" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5361,7 +5361,7 @@
         <v>133883471</v>
       </c>
       <c r="B49" t="n">
-        <v>93257</v>
+        <v>93264</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5458,7 +5458,7 @@
         <v>133883250</v>
       </c>
       <c r="B50" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>133883465</v>
       </c>
       <c r="B51" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5659,32 +5659,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133883252</v>
+        <v>133883457</v>
       </c>
       <c r="B52" t="n">
-        <v>79359</v>
+        <v>99188</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5694,10 +5694,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>521347</v>
+        <v>521412</v>
       </c>
       <c r="R52" t="n">
-        <v>6953820</v>
+        <v>6954018</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5730,6 +5730,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>15st bladrosetter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5756,32 +5761,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133883275</v>
+        <v>133883281</v>
       </c>
       <c r="B53" t="n">
-        <v>79978</v>
+        <v>99188</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5791,10 +5796,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>521472</v>
+        <v>521518</v>
       </c>
       <c r="R53" t="n">
-        <v>6953894</v>
+        <v>6954017</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5853,32 +5858,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133883259</v>
+        <v>133883275</v>
       </c>
       <c r="B54" t="n">
-        <v>101389</v>
+        <v>79985</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>222498</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5888,10 +5893,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>521380</v>
+        <v>521472</v>
       </c>
       <c r="R54" t="n">
-        <v>6953811</v>
+        <v>6953894</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5950,32 +5955,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133883281</v>
+        <v>133883252</v>
       </c>
       <c r="B55" t="n">
-        <v>99181</v>
+        <v>79366</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5985,10 +5990,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>521518</v>
+        <v>521347</v>
       </c>
       <c r="R55" t="n">
-        <v>6954017</v>
+        <v>6953820</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6047,32 +6052,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133883457</v>
+        <v>133883259</v>
       </c>
       <c r="B56" t="n">
-        <v>99181</v>
+        <v>101396</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6082,10 +6087,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>521412</v>
+        <v>521380</v>
       </c>
       <c r="R56" t="n">
-        <v>6954018</v>
+        <v>6953811</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6118,11 +6123,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>15st bladrosetter</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6149,10 +6149,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133883466</v>
+        <v>133883243</v>
       </c>
       <c r="B57" t="n">
-        <v>79359</v>
+        <v>79123</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6160,21 +6160,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6184,10 +6184,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>521385</v>
+        <v>521416</v>
       </c>
       <c r="R57" t="n">
-        <v>6953844</v>
+        <v>6954025</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6246,32 +6246,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133883243</v>
+        <v>133883282</v>
       </c>
       <c r="B58" t="n">
-        <v>79116</v>
+        <v>99188</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6281,10 +6281,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>521416</v>
+        <v>521518</v>
       </c>
       <c r="R58" t="n">
-        <v>6954025</v>
+        <v>6953983</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6343,32 +6343,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133883282</v>
+        <v>133883466</v>
       </c>
       <c r="B59" t="n">
-        <v>99181</v>
+        <v>79366</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6378,10 +6378,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>521518</v>
+        <v>521385</v>
       </c>
       <c r="R59" t="n">
-        <v>6953983</v>
+        <v>6953844</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6440,32 +6440,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133883247</v>
+        <v>133883258</v>
       </c>
       <c r="B60" t="n">
-        <v>79359</v>
+        <v>99188</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6475,10 +6475,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>521336</v>
+        <v>521357</v>
       </c>
       <c r="R60" t="n">
-        <v>6953943</v>
+        <v>6953811</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6511,6 +6511,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Över 20 plantor</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6537,10 +6542,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133883258</v>
+        <v>133883491</v>
       </c>
       <c r="B61" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6572,10 +6577,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>521357</v>
+        <v>521351</v>
       </c>
       <c r="R61" t="n">
-        <v>6953811</v>
+        <v>6953981</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6612,7 +6617,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Över 20 plantor</t>
+          <t>Minst 40</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6639,32 +6644,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133883491</v>
+        <v>133883247</v>
       </c>
       <c r="B62" t="n">
-        <v>99181</v>
+        <v>79366</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6674,10 +6679,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>521351</v>
+        <v>521336</v>
       </c>
       <c r="R62" t="n">
-        <v>6953981</v>
+        <v>6953943</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6710,11 +6715,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Minst 40</t>
         </is>
       </c>
       <c r="AD62" t="b">

--- a/artfynd/A 20225-2026 artfynd.xlsx
+++ b/artfynd/A 20225-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY77"/>
+  <dimension ref="A1:AY79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133883461</v>
+        <v>133883256</v>
       </c>
       <c r="B2" t="n">
-        <v>99188</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521495</v>
+        <v>521353</v>
       </c>
       <c r="R2" t="n">
-        <v>6953868</v>
+        <v>6953801</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133883256</v>
+        <v>133883467</v>
       </c>
       <c r="B3" t="n">
-        <v>91967</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521353</v>
+        <v>521324</v>
       </c>
       <c r="R3" t="n">
-        <v>6953801</v>
+        <v>6953800</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133883277</v>
+        <v>133883447</v>
       </c>
       <c r="B4" t="n">
-        <v>99188</v>
+        <v>57975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521338</v>
+        <v>521330</v>
       </c>
       <c r="R4" t="n">
-        <v>6953912</v>
+        <v>6953791</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -940,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -966,32 +971,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133883489</v>
+        <v>133883242</v>
       </c>
       <c r="B5" t="n">
-        <v>99188</v>
+        <v>83222</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521314</v>
+        <v>521529</v>
       </c>
       <c r="R5" t="n">
-        <v>6953955</v>
+        <v>6954026</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1045,6 +1050,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1063,10 +1069,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133883456</v>
+        <v>133883470</v>
       </c>
       <c r="B6" t="n">
-        <v>80481</v>
+        <v>83222</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1080,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1104,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521555</v>
+        <v>521285</v>
       </c>
       <c r="R6" t="n">
-        <v>6953861</v>
+        <v>6953964</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,32 +1166,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133883263</v>
+        <v>133883471</v>
       </c>
       <c r="B7" t="n">
-        <v>99188</v>
+        <v>93271</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521802</v>
+        <v>521401</v>
       </c>
       <c r="R7" t="n">
-        <v>6954024</v>
+        <v>6953862</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1231,11 +1237,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ca 10 plantor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,32 +1263,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133883237</v>
+        <v>133883284</v>
       </c>
       <c r="B8" t="n">
-        <v>99188</v>
+        <v>93309</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1298,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521548</v>
+        <v>521587</v>
       </c>
       <c r="R8" t="n">
-        <v>6953980</v>
+        <v>6953983</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,11 +1334,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ca 10 plantor</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,10 +1360,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133883248</v>
+        <v>133883244</v>
       </c>
       <c r="B9" t="n">
-        <v>99188</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1371,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1395,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521340</v>
+        <v>521364</v>
       </c>
       <c r="R9" t="n">
-        <v>6953933</v>
+        <v>6954001</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,11 +1431,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Över 20 plantor</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1466,10 +1457,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133883495</v>
+        <v>133883247</v>
       </c>
       <c r="B10" t="n">
-        <v>99188</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1477,21 +1468,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1501,10 +1492,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521293</v>
+        <v>521336</v>
       </c>
       <c r="R10" t="n">
-        <v>6953926</v>
+        <v>6953943</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,14 +1554,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133883278</v>
+        <v>133883249</v>
       </c>
       <c r="B11" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1598,10 +1589,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521295</v>
+        <v>521358</v>
       </c>
       <c r="R11" t="n">
-        <v>6953965</v>
+        <v>6953923</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1634,6 +1625,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>60 cm lång</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1660,14 +1656,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133883249</v>
+        <v>133883252</v>
       </c>
       <c r="B12" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1695,10 +1691,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521358</v>
+        <v>521347</v>
       </c>
       <c r="R12" t="n">
-        <v>6953923</v>
+        <v>6953820</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1731,11 +1727,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>60 cm lång</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1762,14 +1753,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133883469</v>
+        <v>133883278</v>
       </c>
       <c r="B13" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1797,10 +1788,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521326</v>
+        <v>521295</v>
       </c>
       <c r="R13" t="n">
-        <v>6953902</v>
+        <v>6953965</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1859,14 +1850,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133883468</v>
+        <v>133883466</v>
       </c>
       <c r="B14" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1894,10 +1885,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521363</v>
+        <v>521385</v>
       </c>
       <c r="R14" t="n">
-        <v>6953837</v>
+        <v>6953844</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1956,10 +1947,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133883238</v>
+        <v>133883468</v>
       </c>
       <c r="B15" t="n">
-        <v>99188</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,21 +1958,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1991,10 +1982,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521504</v>
+        <v>521363</v>
       </c>
       <c r="R15" t="n">
-        <v>6953992</v>
+        <v>6953837</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2053,27 +2044,27 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133883472</v>
+        <v>133883469</v>
       </c>
       <c r="B16" t="n">
-        <v>80492</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2088,10 +2079,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>521554</v>
+        <v>521326</v>
       </c>
       <c r="R16" t="n">
-        <v>6953860</v>
+        <v>6953902</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2150,32 +2141,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133883280</v>
+        <v>133883241</v>
       </c>
       <c r="B17" t="n">
-        <v>99188</v>
+        <v>83358</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2185,10 +2176,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>521531</v>
+        <v>521529</v>
       </c>
       <c r="R17" t="n">
-        <v>6954025</v>
+        <v>6954026</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2247,32 +2238,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133883253</v>
+        <v>133883243</v>
       </c>
       <c r="B18" t="n">
-        <v>99188</v>
+        <v>79130</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,10 +2273,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521349</v>
+        <v>521416</v>
       </c>
       <c r="R18" t="n">
-        <v>6953818</v>
+        <v>6954025</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2318,11 +2309,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ca 10 plantor</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2349,10 +2335,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133883467</v>
+        <v>133883275</v>
       </c>
       <c r="B19" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2360,21 +2346,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2370,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>521324</v>
+        <v>521472</v>
       </c>
       <c r="R19" t="n">
-        <v>6953800</v>
+        <v>6953894</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2446,10 +2432,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133883455</v>
+        <v>133883446</v>
       </c>
       <c r="B20" t="n">
-        <v>80481</v>
+        <v>79992</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2457,21 +2443,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2467,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521575</v>
+        <v>521332</v>
       </c>
       <c r="R20" t="n">
-        <v>6953947</v>
+        <v>6953999</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2543,32 +2529,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133883239</v>
+        <v>133883260</v>
       </c>
       <c r="B21" t="n">
-        <v>99188</v>
+        <v>80488</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2578,10 +2564,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521519</v>
+        <v>521547</v>
       </c>
       <c r="R21" t="n">
-        <v>6954006</v>
+        <v>6953862</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2614,6 +2600,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2640,10 +2631,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133883240</v>
+        <v>133883261</v>
       </c>
       <c r="B22" t="n">
-        <v>78375</v>
+        <v>80488</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,21 +2642,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2675,10 +2666,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521525</v>
+        <v>521691</v>
       </c>
       <c r="R22" t="n">
-        <v>6954019</v>
+        <v>6953987</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2711,6 +2702,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2737,32 +2733,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133883496</v>
+        <v>133883279</v>
       </c>
       <c r="B23" t="n">
-        <v>99188</v>
+        <v>80488</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2772,10 +2768,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521496</v>
+        <v>521406</v>
       </c>
       <c r="R23" t="n">
-        <v>6954039</v>
+        <v>6954071</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2808,11 +2804,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2839,10 +2830,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133883446</v>
+        <v>133883455</v>
       </c>
       <c r="B24" t="n">
-        <v>79985</v>
+        <v>80488</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2841,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2865,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>521332</v>
+        <v>521575</v>
       </c>
       <c r="R24" t="n">
-        <v>6953999</v>
+        <v>6953947</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,32 +2927,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133883459</v>
+        <v>133883456</v>
       </c>
       <c r="B25" t="n">
-        <v>99188</v>
+        <v>80488</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2962,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521807</v>
+        <v>521555</v>
       </c>
       <c r="R25" t="n">
-        <v>6954021</v>
+        <v>6953861</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3007,11 +2998,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>24st bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3038,27 +3024,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133883244</v>
+        <v>133883472</v>
       </c>
       <c r="B26" t="n">
-        <v>79366</v>
+        <v>80499</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3073,10 +3059,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>521364</v>
+        <v>521554</v>
       </c>
       <c r="R26" t="n">
-        <v>6954001</v>
+        <v>6953860</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3135,10 +3121,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133883284</v>
+        <v>133883234</v>
       </c>
       <c r="B27" t="n">
-        <v>93302</v>
+        <v>57975</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3146,21 +3132,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3170,10 +3156,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521587</v>
+        <v>521776</v>
       </c>
       <c r="R27" t="n">
-        <v>6953983</v>
+        <v>6954013</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3206,6 +3192,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3232,10 +3223,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133883242</v>
+        <v>133883448</v>
       </c>
       <c r="B28" t="n">
-        <v>83215</v>
+        <v>57975</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3243,21 +3234,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3267,10 +3258,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521529</v>
+        <v>521654</v>
       </c>
       <c r="R28" t="n">
-        <v>6954026</v>
+        <v>6954074</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3305,13 +3296,17 @@
           <t>2026-05-15</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3330,10 +3325,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133883245</v>
+        <v>133883449</v>
       </c>
       <c r="B29" t="n">
-        <v>78375</v>
+        <v>57975</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3341,21 +3336,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3365,10 +3360,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521357</v>
+        <v>521652</v>
       </c>
       <c r="R29" t="n">
-        <v>6953972</v>
+        <v>6954080</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3401,6 +3396,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3427,32 +3427,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133883494</v>
+        <v>133883450</v>
       </c>
       <c r="B30" t="n">
-        <v>99188</v>
+        <v>57975</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3462,10 +3462,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521511</v>
+        <v>521664</v>
       </c>
       <c r="R30" t="n">
-        <v>6953850</v>
+        <v>6954069</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3498,6 +3498,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3524,57 +3529,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133883487</v>
+        <v>133883451</v>
       </c>
       <c r="B31" t="n">
-        <v>99188</v>
+        <v>57975</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kojviken, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521273</v>
+        <v>521703</v>
       </c>
       <c r="R31" t="n">
-        <v>6953919</v>
+        <v>6954046</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3611,7 +3604,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Minst 200</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3620,7 +3613,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3639,32 +3631,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133883254</v>
+        <v>133883452</v>
       </c>
       <c r="B32" t="n">
-        <v>99188</v>
+        <v>57975</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3674,10 +3666,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521351</v>
+        <v>521714</v>
       </c>
       <c r="R32" t="n">
-        <v>6953815</v>
+        <v>6954038</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3714,7 +3706,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>20 plantor ca</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3741,27 +3733,27 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133883497</v>
+        <v>133883453</v>
       </c>
       <c r="B33" t="n">
-        <v>57165</v>
+        <v>57975</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102613</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3770,28 +3762,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>ruvande</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kojviken, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521278</v>
+        <v>521710</v>
       </c>
       <c r="R33" t="n">
-        <v>6953952</v>
+        <v>6954038</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3824,6 +3804,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3850,32 +3835,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133883458</v>
+        <v>133883454</v>
       </c>
       <c r="B34" t="n">
-        <v>99188</v>
+        <v>57975</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3885,10 +3870,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>521417</v>
+        <v>521722</v>
       </c>
       <c r="R34" t="n">
-        <v>6954029</v>
+        <v>6954031</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3925,7 +3910,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>21st bladrosetter</t>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3952,32 +3937,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133883490</v>
+        <v>133883475</v>
       </c>
       <c r="B35" t="n">
-        <v>99188</v>
+        <v>57975</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3987,10 +3972,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>521336</v>
+        <v>521308</v>
       </c>
       <c r="R35" t="n">
-        <v>6953957</v>
+        <v>6953817</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4027,7 +4012,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Minst 50</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4054,32 +4039,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133883484</v>
+        <v>133883476</v>
       </c>
       <c r="B36" t="n">
-        <v>99188</v>
+        <v>57975</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4089,10 +4074,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>521420</v>
+        <v>521309</v>
       </c>
       <c r="R36" t="n">
-        <v>6953892</v>
+        <v>6953828</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4125,6 +4110,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4151,32 +4141,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133883488</v>
+        <v>133883477</v>
       </c>
       <c r="B37" t="n">
-        <v>99188</v>
+        <v>57975</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4186,10 +4176,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>521301</v>
+        <v>521295</v>
       </c>
       <c r="R37" t="n">
-        <v>6953960</v>
+        <v>6953845</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4222,6 +4212,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4248,10 +4243,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133883260</v>
+        <v>133883479</v>
       </c>
       <c r="B38" t="n">
-        <v>80481</v>
+        <v>57975</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4259,21 +4254,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4283,10 +4278,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>521547</v>
+        <v>521274</v>
       </c>
       <c r="R38" t="n">
-        <v>6953862</v>
+        <v>6953884</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4323,7 +4318,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4350,10 +4345,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133883241</v>
+        <v>133883480</v>
       </c>
       <c r="B39" t="n">
-        <v>83351</v>
+        <v>57975</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4361,21 +4356,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4385,10 +4380,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>521529</v>
+        <v>521272</v>
       </c>
       <c r="R39" t="n">
-        <v>6954026</v>
+        <v>6953892</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4421,6 +4416,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4447,10 +4447,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133883279</v>
+        <v>133883481</v>
       </c>
       <c r="B40" t="n">
-        <v>80481</v>
+        <v>57975</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4458,21 +4458,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4482,10 +4482,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>521406</v>
+        <v>521264</v>
       </c>
       <c r="R40" t="n">
-        <v>6954071</v>
+        <v>6953906</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4518,6 +4518,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4544,32 +4549,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133883493</v>
+        <v>133883482</v>
       </c>
       <c r="B41" t="n">
-        <v>99188</v>
+        <v>57975</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4579,10 +4584,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>521488</v>
+        <v>521755</v>
       </c>
       <c r="R41" t="n">
-        <v>6954062</v>
+        <v>6954023</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4615,6 +4620,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4641,57 +4651,45 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133883463</v>
+        <v>133883483</v>
       </c>
       <c r="B42" t="n">
-        <v>99188</v>
+        <v>57975</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kojviken, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>521538</v>
+        <v>521749</v>
       </c>
       <c r="R42" t="n">
-        <v>6953983</v>
+        <v>6954025</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4728,7 +4726,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>&gt;100st bladrosetter</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4737,7 +4735,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4756,45 +4753,57 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133883261</v>
+        <v>133883497</v>
       </c>
       <c r="B43" t="n">
-        <v>80481</v>
+        <v>57165</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>102613</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>ruvande</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Kojviken, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>521691</v>
+        <v>521278</v>
       </c>
       <c r="R43" t="n">
-        <v>6953987</v>
+        <v>6953952</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4827,11 +4836,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4858,32 +4862,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133883470</v>
+        <v>133883237</v>
       </c>
       <c r="B44" t="n">
-        <v>83215</v>
+        <v>99195</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4893,10 +4897,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>521285</v>
+        <v>521548</v>
       </c>
       <c r="R44" t="n">
-        <v>6953964</v>
+        <v>6953980</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4929,6 +4933,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ca 10 plantor</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4955,10 +4964,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133883460</v>
+        <v>133883238</v>
       </c>
       <c r="B45" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4990,10 +4999,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>521807</v>
+        <v>521504</v>
       </c>
       <c r="R45" t="n">
-        <v>6954020</v>
+        <v>6953992</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5026,11 +5035,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5057,10 +5061,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133883246</v>
+        <v>133883239</v>
       </c>
       <c r="B46" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5092,10 +5096,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>521328</v>
+        <v>521519</v>
       </c>
       <c r="R46" t="n">
-        <v>6953954</v>
+        <v>6954006</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5128,11 +5132,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>7 plantor</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5159,10 +5158,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133883486</v>
+        <v>133883246</v>
       </c>
       <c r="B47" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5194,10 +5193,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>521407</v>
+        <v>521328</v>
       </c>
       <c r="R47" t="n">
-        <v>6953853</v>
+        <v>6953954</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5230,6 +5229,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>7 plantor</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5256,10 +5260,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133883462</v>
+        <v>133883248</v>
       </c>
       <c r="B48" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5291,10 +5295,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>521356</v>
+        <v>521340</v>
       </c>
       <c r="R48" t="n">
-        <v>6954020</v>
+        <v>6953933</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5331,7 +5335,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>7st bladrosetter</t>
+          <t>Över 20 plantor</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5358,32 +5362,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133883471</v>
+        <v>133883250</v>
       </c>
       <c r="B49" t="n">
-        <v>93264</v>
+        <v>99195</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5393,10 +5397,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>521401</v>
+        <v>521352</v>
       </c>
       <c r="R49" t="n">
-        <v>6953862</v>
+        <v>6953865</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5429,6 +5433,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Över 10 plantor</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5455,10 +5464,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133883250</v>
+        <v>133883253</v>
       </c>
       <c r="B50" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5490,10 +5499,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>521352</v>
+        <v>521349</v>
       </c>
       <c r="R50" t="n">
-        <v>6953865</v>
+        <v>6953818</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5530,7 +5539,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Över 10 plantor</t>
+          <t>Ca 10 plantor</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5557,10 +5566,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133883465</v>
+        <v>133883254</v>
       </c>
       <c r="B51" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5592,10 +5601,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>521548</v>
+        <v>521351</v>
       </c>
       <c r="R51" t="n">
-        <v>6953962</v>
+        <v>6953815</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5632,7 +5641,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>3st bladrosetter</t>
+          <t>20 plantor ca</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5659,10 +5668,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133883457</v>
+        <v>133883258</v>
       </c>
       <c r="B52" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5694,10 +5703,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>521412</v>
+        <v>521357</v>
       </c>
       <c r="R52" t="n">
-        <v>6954018</v>
+        <v>6953811</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5734,7 +5743,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>15st bladrosetter</t>
+          <t>Över 20 plantor</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5761,10 +5770,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133883281</v>
+        <v>133883263</v>
       </c>
       <c r="B53" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5796,10 +5805,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>521518</v>
+        <v>521802</v>
       </c>
       <c r="R53" t="n">
-        <v>6954017</v>
+        <v>6954024</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5832,6 +5841,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ca 10 plantor</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5858,32 +5872,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133883275</v>
+        <v>133883277</v>
       </c>
       <c r="B54" t="n">
-        <v>79985</v>
+        <v>99195</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5893,10 +5907,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>521472</v>
+        <v>521338</v>
       </c>
       <c r="R54" t="n">
-        <v>6953894</v>
+        <v>6953912</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5955,32 +5969,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133883252</v>
+        <v>133883280</v>
       </c>
       <c r="B55" t="n">
-        <v>79366</v>
+        <v>99195</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5990,10 +6004,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>521347</v>
+        <v>521531</v>
       </c>
       <c r="R55" t="n">
-        <v>6953820</v>
+        <v>6954025</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6052,32 +6066,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133883259</v>
+        <v>133883281</v>
       </c>
       <c r="B56" t="n">
-        <v>101396</v>
+        <v>99195</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6087,10 +6101,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>521380</v>
+        <v>521518</v>
       </c>
       <c r="R56" t="n">
-        <v>6953811</v>
+        <v>6954017</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6149,32 +6163,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133883243</v>
+        <v>133883282</v>
       </c>
       <c r="B57" t="n">
-        <v>79123</v>
+        <v>99195</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6184,10 +6198,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>521416</v>
+        <v>521518</v>
       </c>
       <c r="R57" t="n">
-        <v>6954025</v>
+        <v>6953983</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6246,10 +6260,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133883282</v>
+        <v>133883457</v>
       </c>
       <c r="B58" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6281,10 +6295,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>521518</v>
+        <v>521412</v>
       </c>
       <c r="R58" t="n">
-        <v>6953983</v>
+        <v>6954018</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6317,6 +6331,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>15st bladrosetter</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6343,32 +6362,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133883466</v>
+        <v>133883458</v>
       </c>
       <c r="B59" t="n">
-        <v>79366</v>
+        <v>99195</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6378,10 +6397,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>521385</v>
+        <v>521417</v>
       </c>
       <c r="R59" t="n">
-        <v>6953844</v>
+        <v>6954029</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6414,6 +6433,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>21st bladrosetter</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6440,10 +6464,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133883258</v>
+        <v>133883459</v>
       </c>
       <c r="B60" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6475,10 +6499,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>521357</v>
+        <v>521807</v>
       </c>
       <c r="R60" t="n">
-        <v>6953811</v>
+        <v>6954021</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6515,7 +6539,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Över 20 plantor</t>
+          <t>24st bladrosetter</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6542,10 +6566,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133883491</v>
+        <v>133883460</v>
       </c>
       <c r="B61" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6577,10 +6601,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>521351</v>
+        <v>521807</v>
       </c>
       <c r="R61" t="n">
-        <v>6953981</v>
+        <v>6954020</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6617,7 +6641,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Minst 40</t>
+          <t>5st bladrosetter</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6644,32 +6668,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133883247</v>
+        <v>133883461</v>
       </c>
       <c r="B62" t="n">
-        <v>79366</v>
+        <v>99195</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6679,10 +6703,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>521336</v>
+        <v>521495</v>
       </c>
       <c r="R62" t="n">
-        <v>6953943</v>
+        <v>6953868</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6741,32 +6765,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133883454</v>
+        <v>133883462</v>
       </c>
       <c r="B63" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6776,10 +6800,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>521722</v>
+        <v>521356</v>
       </c>
       <c r="R63" t="n">
-        <v>6954031</v>
+        <v>6954020</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6816,7 +6840,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>7st bladrosetter</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6843,45 +6867,57 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133883477</v>
+        <v>133883463</v>
       </c>
       <c r="B64" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Kojviken, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>521295</v>
+        <v>521538</v>
       </c>
       <c r="R64" t="n">
-        <v>6953845</v>
+        <v>6953983</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6918,7 +6954,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>&gt;100st bladrosetter</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6927,6 +6963,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -6945,32 +6982,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133883447</v>
+        <v>133883465</v>
       </c>
       <c r="B65" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6980,10 +7017,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>521330</v>
+        <v>521548</v>
       </c>
       <c r="R65" t="n">
-        <v>6953791</v>
+        <v>6953962</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7020,7 +7057,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>3st bladrosetter</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7047,32 +7084,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133883479</v>
+        <v>133883484</v>
       </c>
       <c r="B66" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7082,10 +7119,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>521274</v>
+        <v>521420</v>
       </c>
       <c r="R66" t="n">
-        <v>6953884</v>
+        <v>6953892</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7118,11 +7155,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7149,32 +7181,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133883453</v>
+        <v>133883486</v>
       </c>
       <c r="B67" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7184,10 +7216,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>521710</v>
+        <v>521407</v>
       </c>
       <c r="R67" t="n">
-        <v>6954038</v>
+        <v>6953853</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7220,11 +7252,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7251,45 +7278,57 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133883448</v>
+        <v>133883487</v>
       </c>
       <c r="B68" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Kojviken, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>521654</v>
+        <v>521273</v>
       </c>
       <c r="R68" t="n">
-        <v>6954074</v>
+        <v>6953919</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7326,7 +7365,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Minst 200</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7335,6 +7374,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7353,32 +7393,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133883452</v>
+        <v>133883488</v>
       </c>
       <c r="B69" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7388,10 +7428,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>521714</v>
+        <v>521301</v>
       </c>
       <c r="R69" t="n">
-        <v>6954038</v>
+        <v>6953960</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7424,11 +7464,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7455,32 +7490,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133883234</v>
+        <v>133883489</v>
       </c>
       <c r="B70" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7490,10 +7525,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>521776</v>
+        <v>521314</v>
       </c>
       <c r="R70" t="n">
-        <v>6954013</v>
+        <v>6953955</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7526,11 +7561,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på gran</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7557,32 +7587,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133883449</v>
+        <v>133883490</v>
       </c>
       <c r="B71" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7592,10 +7622,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>521652</v>
+        <v>521336</v>
       </c>
       <c r="R71" t="n">
-        <v>6954080</v>
+        <v>6953957</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7632,7 +7662,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7659,32 +7689,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133883476</v>
+        <v>133883491</v>
       </c>
       <c r="B72" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7694,10 +7724,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>521309</v>
+        <v>521351</v>
       </c>
       <c r="R72" t="n">
-        <v>6953828</v>
+        <v>6953981</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7734,7 +7764,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Minst 40</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7761,32 +7791,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133883480</v>
+        <v>133883493</v>
       </c>
       <c r="B73" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7796,10 +7826,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>521272</v>
+        <v>521488</v>
       </c>
       <c r="R73" t="n">
-        <v>6953892</v>
+        <v>6954062</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7832,11 +7862,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7863,32 +7888,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133883450</v>
+        <v>133883494</v>
       </c>
       <c r="B74" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7898,10 +7923,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>521664</v>
+        <v>521511</v>
       </c>
       <c r="R74" t="n">
-        <v>6954069</v>
+        <v>6953850</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7934,11 +7959,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7965,32 +7985,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133883451</v>
+        <v>133883495</v>
       </c>
       <c r="B75" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8000,10 +8020,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>521703</v>
+        <v>521293</v>
       </c>
       <c r="R75" t="n">
-        <v>6954046</v>
+        <v>6953926</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8036,11 +8056,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8067,32 +8082,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133883483</v>
+        <v>133883496</v>
       </c>
       <c r="B76" t="n">
-        <v>57975</v>
+        <v>99195</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8102,10 +8117,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>521749</v>
+        <v>521496</v>
       </c>
       <c r="R76" t="n">
-        <v>6954025</v>
+        <v>6954039</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8142,7 +8157,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Minst 50</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8169,32 +8184,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133883482</v>
+        <v>133883259</v>
       </c>
       <c r="B77" t="n">
-        <v>57975</v>
+        <v>101403</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8204,10 +8219,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>521755</v>
+        <v>521380</v>
       </c>
       <c r="R77" t="n">
-        <v>6954023</v>
+        <v>6953811</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8242,11 +8257,6 @@
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8268,6 +8278,200 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>133883240</v>
+      </c>
+      <c r="B78" t="n">
+        <v>78382</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Kojviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>521525</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6954019</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>133883245</v>
+      </c>
+      <c r="B79" t="n">
+        <v>78382</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Kojviken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>521357</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6953972</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20225-2026 artfynd.xlsx
+++ b/artfynd/A 20225-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY79"/>
+  <dimension ref="A1:AZ79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883256</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883242</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883470</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883471</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1158,6 +1183,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883284</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1255,6 +1285,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883244</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1352,6 +1387,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883247</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1454,6 +1494,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883249</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1551,6 +1596,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883252</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1648,6 +1698,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883278</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1745,6 +1800,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883466</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1842,6 +1902,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883467</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1939,6 +2004,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883468</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2036,6 +2106,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883469</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2133,6 +2208,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883241</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2230,6 +2310,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883243</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2327,6 +2412,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883275</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2424,6 +2514,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883446</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2526,6 +2621,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883260</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2628,6 +2728,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883261</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2725,6 +2830,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883279</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2822,6 +2932,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883455</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2919,6 +3034,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883456</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3016,6 +3136,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883472</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3118,6 +3243,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883234</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3220,6 +3350,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883447</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3322,6 +3457,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883448</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3424,6 +3564,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883449</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3526,6 +3671,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883450</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3628,6 +3778,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883451</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3730,6 +3885,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883452</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3832,6 +3992,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883453</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3934,6 +4099,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883454</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4036,6 +4206,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883475</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4138,6 +4313,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883476</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4240,6 +4420,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883477</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4342,6 +4527,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883479</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4444,6 +4634,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883480</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4546,6 +4741,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883481</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4648,6 +4848,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883482</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4750,6 +4955,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883483</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4859,6 +5069,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883497</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4961,6 +5176,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883237</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5058,6 +5278,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883238</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5155,6 +5380,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883239</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5257,6 +5487,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883246</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5359,6 +5594,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883248</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5461,6 +5701,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883250</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5563,6 +5808,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883253</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5665,6 +5915,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883254</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5767,6 +6022,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883258</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5869,6 +6129,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883263</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5966,6 +6231,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883277</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6063,6 +6333,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883280</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6160,6 +6435,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883281</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6257,6 +6537,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883282</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6359,6 +6644,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883457</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6461,6 +6751,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883458</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6563,6 +6858,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883459</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6665,6 +6965,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883460</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6762,6 +7067,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883461</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6864,6 +7174,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883462</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6979,6 +7294,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883463</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7081,6 +7401,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883465</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7178,6 +7503,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883484</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7275,6 +7605,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883486</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7390,6 +7725,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883487</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7487,6 +7827,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883488</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7584,6 +7929,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883489</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7686,6 +8036,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883490</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7788,6 +8143,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883491</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7885,6 +8245,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883493</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7982,6 +8347,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883494</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8079,6 +8449,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883495</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8181,6 +8556,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883496</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8278,6 +8658,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883259</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8375,6 +8760,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883240</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8472,8 +8862,93 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133883245</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>